--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T13:26:37+00:00</t>
+    <t>2025-01-24T17:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T17:22:23+00:00</t>
+    <t>2025-01-29T14:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T14:25:50+00:00</t>
+    <t>2025-01-29T15:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T15:50:40+00:00</t>
+    <t>2025-01-30T15:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T15:03:39+00:00</t>
+    <t>2025-01-31T08:45:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="144">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T08:45:39+00:00</t>
+    <t>2025-02-18T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,6 +260,12 @@
     <t>Identifiant unique du document.</t>
   </si>
   <si>
+    <t>EnteteDocument.modeleDocument</t>
+  </si>
+  <si>
+    <t>Modèle du document et version du modèle.</t>
+  </si>
+  <si>
     <t>EnteteDocument.typeDocument</t>
   </si>
   <si>
@@ -270,6 +276,16 @@
     <t>Type de document.</t>
   </si>
   <si>
+    <t>EnteteDocument.titreDocument</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Titre du document.</t>
+  </si>
+  <si>
     <t>EnteteDocument.dateDeCreation</t>
   </si>
   <si>
@@ -299,10 +315,6 @@
   </si>
   <si>
     <t>EnteteDocument.versionDocument</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>Numéro de version du document.</t>
@@ -753,7 +765,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ24"/>
+  <dimension ref="A1:AJ26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.1640625" customWidth="true" bestFit="true"/>
@@ -1131,13 +1143,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="L4" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="M4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1205,10 +1217,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1231,13 +1243,13 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L5" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="M5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1288,7 +1300,7 @@
         <v>72</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -1305,10 +1317,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1331,7 +1343,7 @@
         <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="L6" t="s" s="2">
         <v>88</v>
@@ -1388,7 +1400,7 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -1431,13 +1443,13 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1505,10 +1517,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1531,13 +1543,13 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1588,7 +1600,7 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -1605,10 +1617,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1631,7 +1643,7 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="L9" t="s" s="2">
         <v>95</v>
@@ -1688,7 +1700,7 @@
         <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -1731,7 +1743,7 @@
         <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L10" t="s" s="2">
         <v>97</v>
@@ -1831,13 +1843,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="L11" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="M11" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1905,10 +1917,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1919,7 +1931,7 @@
         <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>72</v>
@@ -1931,13 +1943,13 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1988,13 +2000,13 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>72</v>
@@ -2005,10 +2017,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2016,10 +2028,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>72</v>
@@ -2031,13 +2043,13 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2088,13 +2100,13 @@
         <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>72</v>
@@ -2105,10 +2117,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2119,7 +2131,7 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>72</v>
@@ -2131,13 +2143,13 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2188,13 +2200,13 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>72</v>
@@ -2205,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2231,13 +2243,13 @@
         <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2288,7 +2300,7 @@
         <v>72</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>73</v>
@@ -2305,10 +2317,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2331,13 +2343,13 @@
         <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2388,7 +2400,7 @@
         <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -2405,10 +2417,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2431,13 +2443,13 @@
         <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2488,7 +2500,7 @@
         <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>73</v>
@@ -2505,10 +2517,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2516,7 +2528,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>78</v>
@@ -2531,13 +2543,13 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2588,10 +2600,10 @@
         <v>72</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>78</v>
@@ -2605,10 +2617,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2631,13 +2643,13 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2688,7 +2700,7 @@
         <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>73</v>
@@ -2705,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2716,7 +2728,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>78</v>
@@ -2731,13 +2743,13 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2788,10 +2800,10 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>78</v>
@@ -2805,10 +2817,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2816,7 +2828,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>74</v>
@@ -2831,13 +2843,13 @@
         <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2888,10 +2900,10 @@
         <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>74</v>
@@ -2905,10 +2917,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2916,7 +2928,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>78</v>
@@ -2931,13 +2943,13 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -2988,10 +3000,10 @@
         <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>78</v>
@@ -3005,10 +3017,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3016,7 +3028,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>74</v>
@@ -3031,13 +3043,13 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3088,10 +3100,10 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>74</v>
@@ -3105,10 +3117,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3116,7 +3128,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>78</v>
@@ -3131,13 +3143,13 @@
         <v>72</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3188,10 +3200,10 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>78</v>
@@ -3200,6 +3212,206 @@
         <v>72</v>
       </c>
       <c r="AJ24" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>1- Modèle logique métier de l'en-tête</t>
+    <t>Modèle logique métier de l'en-tête</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T15:18:09+00:00</t>
+    <t>2025-02-23T14:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Eléments de l'en-tête contenat les données d'indentification du document.</t>
+    <t>Eléments de l'entête d'un document contenant les données les informations générales et nécessaires à la gestion du document (identification et type du document, patient/usager, auteur, évènement documenté, etc...</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -326,74 +326,24 @@
     <t>Statut du document.</t>
   </si>
   <si>
-    <t>EnteteDocument.patientDocument</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/PatientDocument
+    <t>EnteteDocument.patient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Patient
 </t>
   </si>
   <si>
-    <t>1.1- Patient / Usager.</t>
-  </si>
-  <si>
-    <t>EnteteDocument.auteurDocument</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/AuteurDocument
+    <t>Patient / Usager.</t>
+  </si>
+  <si>
+    <t>EnteteDocument.auteur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Auteur
 </t>
   </si>
   <si>
-    <t>1.2- Auteur du document.</t>
-  </si>
-  <si>
-    <t>EnteteDocument.informateurDocument</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/InformateurDocument
-</t>
-  </si>
-  <si>
-    <t>1.3- Informateur (informant), ayant fourni des informations utiles aux actes en rapport avec la production du document.</t>
-  </si>
-  <si>
-    <t>EnteteDocument.structureConservationDocument</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/StructureConservationDocument
-</t>
-  </si>
-  <si>
-    <t>1.4- Structure chargée de la conservation du document.</t>
-  </si>
-  <si>
-    <t>EnteteDocument.destinataireDocument</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/DestinatairePrevuDocument
-</t>
-  </si>
-  <si>
-    <t>1.5- Destinataire prévu du document.</t>
-  </si>
-  <si>
-    <t>EnteteDocument.responsableDocuement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/ResponsableDocument
-</t>
-  </si>
-  <si>
-    <t>1.6- Responsable du document.</t>
-  </si>
-  <si>
-    <t>EnteteDocument.validateurDocument</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/ValidateurDocument
-</t>
-  </si>
-  <si>
-    <t>1.7- Professionnel attestant la validité du contenu du document.</t>
+    <t>Auteur du document.</t>
   </si>
   <si>
     <t>EnteteDocument.operateurSaisie</t>
@@ -403,17 +353,67 @@
 </t>
   </si>
   <si>
-    <t>1.8- Opérateur de saisie.</t>
+    <t>Opérateur de saisie.</t>
+  </si>
+  <si>
+    <t>EnteteDocument.informateur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Informateur
+</t>
+  </si>
+  <si>
+    <t>Informateur ayant fourni des informations utiles à la production du document.</t>
+  </si>
+  <si>
+    <t>EnteteDocument.structureConservation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/StructureConservation
+</t>
+  </si>
+  <si>
+    <t>Structure chargée de la conservation du document.</t>
+  </si>
+  <si>
+    <t>EnteteDocument.destinataire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/DestinatairePrevu
+</t>
+  </si>
+  <si>
+    <t>Destinataire prévu du document.</t>
+  </si>
+  <si>
+    <t>EnteteDocument.responsable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Responsable
+</t>
+  </si>
+  <si>
+    <t>Responsable du document.</t>
+  </si>
+  <si>
+    <t>EnteteDocument.validateur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Validateur
+</t>
+  </si>
+  <si>
+    <t>Professionnel attestant la validité du contenu du document.</t>
   </si>
   <si>
     <t>EnteteDocument.participant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/ParticipantDocument
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Participant
 </t>
   </si>
   <si>
-    <t>1.9- Participant, différent de l'auteur, du responsable, de l'opérateur de saisie, de l'informateur ou du destinataire.</t>
+    <t>Participant, différent de l'auteur, du responsable, de l'opérateur de saisie, de l'informateur ou du destinataire.</t>
   </si>
   <si>
     <t>EnteteDocument.associationPrescription</t>
@@ -423,17 +423,17 @@
 </t>
   </si>
   <si>
-    <t>1.10- Association du document à une prescription.</t>
-  </si>
-  <si>
-    <t>EnteteDocument.evenementDocumente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/EvenementDocumente
+    <t>Association du document à une prescription.</t>
+  </si>
+  <si>
+    <t>EnteteDocument.evenement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Evenement
 </t>
   </si>
   <si>
-    <t>1.11- Evènement documenté et notamment le cadre d'exercice.</t>
+    <t>Evènement documenté et notamment le cadre d'exercice.</t>
   </si>
   <si>
     <t>EnteteDocument.documentReference</t>
@@ -443,17 +443,17 @@
 </t>
   </si>
   <si>
-    <t>1.12- Document de référence.</t>
-  </si>
-  <si>
-    <t>EnteteDocument.consentementAssocieAuDocument</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/ConsentementDocument
+    <t>Document de référence (à remplacer, transformé, …).</t>
+  </si>
+  <si>
+    <t>EnteteDocument.consentementAssocie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Consentement
 </t>
   </si>
   <si>
-    <t>1.13- Consentement associé au document.</t>
+    <t>Consentement associé au document.</t>
   </si>
   <si>
     <t>EnteteDocument.associationPriseEncharge</t>
@@ -463,7 +463,7 @@
 </t>
   </si>
   <si>
-    <t>1.14- Association du document à une prise en charge.</t>
+    <t>Association du document à une prise en charge.</t>
   </si>
 </sst>
 </file>
@@ -768,8 +768,8 @@
   <dimension ref="A1:AJ26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.1640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.1640625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.453125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -778,7 +778,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="93.72265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="87.0859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -799,7 +799,7 @@
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="49.1640625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="42.453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -2231,7 +2231,7 @@
         <v>73</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>72</v>
@@ -2306,7 +2306,7 @@
         <v>73</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>72</v>
@@ -2328,10 +2328,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>72</v>
@@ -2403,10 +2403,10 @@
         <v>111</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>72</v>
@@ -2428,10 +2428,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>72</v>
@@ -2503,10 +2503,10 @@
         <v>114</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>72</v>
@@ -2528,10 +2528,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>72</v>
@@ -2603,10 +2603,10 @@
         <v>117</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>72</v>
@@ -2628,10 +2628,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>72</v>
@@ -2703,10 +2703,10 @@
         <v>120</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>72</v>
@@ -2731,7 +2731,7 @@
         <v>73</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>72</v>
@@ -2806,7 +2806,7 @@
         <v>73</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>72</v>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:02:58+00:00</t>
+    <t>2025-02-24T10:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:33:29+00:00</t>
+    <t>2025-02-24T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:08:59+00:00</t>
+    <t>2025-02-24T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T14:08:41+00:00</t>
+    <t>2025-02-25T09:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
